--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484768_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484768_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1205</v>
+        <v>0.7488</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3834</v>
+        <v>1.0911</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.263</v>
+        <v>-0.3423</v>
       </c>
       <c r="G2" t="n">
         <v>0.5949</v>
@@ -610,13 +610,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5255</v>
+        <v>0.1539</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4144</v>
+        <v>0.1221</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1111</v>
+        <v>0.0318</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.6912</v>
+        <v>-1.7109</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7255</v>
+        <v>2.1556</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.4167</v>
+        <v>-3.8664</v>
       </c>
       <c r="G4" t="n">
         <v>0.9661999999999999</v>
@@ -766,13 +766,13 @@
         <v>2.2644</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1286</v>
+        <v>-1.1483</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0923</v>
+        <v>-0.6623</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0363</v>
+        <v>-0.4861</v>
       </c>
       <c r="V4" t="n">
         <v>0.9244</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.6149</v>
+        <v>-2.562</v>
       </c>
       <c r="E5" t="n">
         <v>-1.9123</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7026</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5157</v>
@@ -844,13 +844,13 @@
         <v>0.1887</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4009</v>
+        <v>-0.348</v>
       </c>
       <c r="T5" t="n">
         <v>-0.0465</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3545</v>
+        <v>-0.3016</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.0456</v>
+        <v>-3.7797</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6856</v>
+        <v>-1.3933</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.36</v>
+        <v>-2.3864</v>
       </c>
       <c r="G6" t="n">
         <v>-3.8516</v>
@@ -922,13 +922,13 @@
         <v>0.7548</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9488</v>
+        <v>-0.6829</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5755</v>
+        <v>-0.2832</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3733</v>
+        <v>-0.3997</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. BLEDA MIRANDA</t>
+          <t>G. TUDELA GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.253</v>
+        <v>-4.3839</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3441</v>
+        <v>0.3752</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.9089</v>
+        <v>-4.7591</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.5045</v>
+        <v>-0.7693</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.0435</v>
+        <v>-0.8475</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4609</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2822</v>
+        <v>2.9592</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1589</v>
+        <v>2.7946</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1234</v>
+        <v>0.1645</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.7867</v>
+        <v>-3.7284</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.2024</v>
+        <v>-3.6422</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5843</v>
+        <v>-0.0863</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1322</v>
+        <v>1.887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6355</v>
+        <v>-0.8034</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0152</v>
+        <v>-0.3761</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.4273</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2452</v>
+        <v>-2.8112</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.3208</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6036</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. TUDELA GARCIA</t>
+          <t>C. BLEDA MIRANDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.2835</v>
+        <v>-4.5007</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2375</v>
+        <v>-0.539</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.521</v>
+        <v>-3.9618</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7693</v>
+        <v>-3.5045</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8475</v>
+        <v>-3.0435</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07829999999999999</v>
+        <v>-0.4609</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9592</v>
+        <v>0.2822</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7946</v>
+        <v>0.1589</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1645</v>
+        <v>0.1234</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.7284</v>
+        <v>-3.7867</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.6422</v>
+        <v>-3.2024</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0863</v>
+        <v>-0.5843</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.887</v>
+        <v>1.1322</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.703</v>
+        <v>-0.8833</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5139</v>
+        <v>-0.1796</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1892</v>
+        <v>-0.7036</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.8112</v>
+        <v>-1.2452</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3208</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4904</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. ALBERT ABELLAN</t>
+          <t>S. MASSAMBA JOHANSSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4927</v>
+        <v>-4.7443</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2594</v>
+        <v>-2.9394</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2333</v>
+        <v>-1.8048</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1293</v>
+        <v>-2.1432</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3061</v>
+        <v>-1.1019</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-1.0413</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2736</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8806</v>
+        <v>0.7028</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.607</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4029</v>
+        <v>-2.2375</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.1867</v>
+        <v>-1.8047</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2162</v>
+        <v>-0.4329</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.887</v>
+        <v>-3.2079</v>
       </c>
       <c r="Q9" t="n">
         <v>-3.774</v>
       </c>
       <c r="R9" t="n">
-        <v>1.887</v>
+        <v>0.5661</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1746</v>
+        <v>-0.6574</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2409</v>
+        <v>-0.1842</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4156</v>
+        <v>-0.4732</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3018</v>
+        <v>1.2642</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3018</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. MASSAMBA JOHANSSON</t>
+          <t>F. ALBERT ABELLAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0063</v>
+        <v>-4.7867</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0956</v>
+        <v>-2.7651</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9107</v>
+        <v>-2.0216</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1432</v>
+        <v>-2.1293</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1019</v>
+        <v>-1.3061</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0413</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.09429999999999999</v>
+        <v>1.2736</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7028</v>
+        <v>1.8806</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.607</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2375</v>
+        <v>-3.4029</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8047</v>
+        <v>-3.1867</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4329</v>
+        <v>-0.2162</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.2079</v>
+        <v>-1.887</v>
       </c>
       <c r="Q10" t="n">
         <v>-3.774</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5661</v>
+        <v>1.887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9194</v>
+        <v>-0.4687</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3404</v>
+        <v>-0.2647</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.579</v>
+        <v>-0.2039</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2642</v>
+        <v>-0.3018</v>
       </c>
       <c r="W10" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3398</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.5697</v>
+        <v>-5.0456</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3668</v>
+        <v>-3.0544</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2029</v>
+        <v>-1.9913</v>
       </c>
       <c r="G11" t="n">
         <v>-5.9577</v>
@@ -1312,13 +1312,13 @@
         <v>0.7548</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7066</v>
+        <v>-0.1825</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3281</v>
+        <v>-0.0156</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3786</v>
+        <v>-0.1669</v>
       </c>
       <c r="V11" t="n">
         <v>0.3398</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4403</v>
+        <v>-5.9956</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7113</v>
+        <v>-2.3988</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.729</v>
+        <v>-3.5967</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7125</v>
@@ -1390,13 +1390,13 @@
         <v>0.9435</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.539</v>
+        <v>-1.0943</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5168</v>
+        <v>-0.2043</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0222</v>
+        <v>-0.89</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3018</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.3095</v>
+        <v>-6.6498</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1025</v>
+        <v>-1.575</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.207</v>
+        <v>-5.0748</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0958</v>
@@ -1468,13 +1468,13 @@
         <v>1.887</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7988</v>
+        <v>-1.1391</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2345</v>
+        <v>-0.7071</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5643</v>
+        <v>-0.432</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4714</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-44.2692</v>
+        <v>-43.0934</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.8142</v>
+        <v>-12.6384</v>
       </c>
       <c r="F14" t="n">
-        <v>-30.4551</v>
+        <v>-30.45489999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-21.8015</v>
@@ -1525,7 +1525,7 @@
         <v>11.6294</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6521999999999998</v>
+        <v>-0.6521999999999993</v>
       </c>
       <c r="M14" t="n">
         <v>-32.7784</v>
@@ -1546,22 +1546,22 @@
         <v>12.2655</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.4297</v>
+        <v>-7.254</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.9775</v>
+        <v>-2.8015</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.4526</v>
+        <v>-4.452500000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.603</v>
+        <v>-4.603000000000001</v>
       </c>
       <c r="W14" t="n">
         <v>0.8864000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.489400000000001</v>
+        <v>-5.4894</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0752</v>
+        <v>8.3094</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8607</v>
+        <v>5.835</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2146</v>
+        <v>2.4744</v>
       </c>
       <c r="G15" t="n">
         <v>6.475</v>
@@ -1624,13 +1624,13 @@
         <v>3.0192</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4115</v>
+        <v>1.6457</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3868</v>
+        <v>0.5875</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7984</v>
+        <v>1.0582</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3757</v>
+        <v>7.3357</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4432</v>
+        <v>4.2227</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9325</v>
+        <v>3.113</v>
       </c>
       <c r="G16" t="n">
         <v>3.1861</v>
@@ -1702,13 +1702,13 @@
         <v>2.6418</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0558</v>
+        <v>0.9041</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4456</v>
+        <v>0.3338</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3898</v>
+        <v>0.5703</v>
       </c>
       <c r="V16" t="n">
         <v>0.6036</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.0923</v>
+        <v>6.6046</v>
       </c>
       <c r="E17" t="n">
-        <v>5.1793</v>
+        <v>5.3742</v>
       </c>
       <c r="F17" t="n">
-        <v>0.913</v>
+        <v>1.2304</v>
       </c>
       <c r="G17" t="n">
         <v>2.133</v>
@@ -1780,13 +1780,13 @@
         <v>2.2644</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4497</v>
+        <v>0.962</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0617</v>
+        <v>0.2566</v>
       </c>
       <c r="U17" t="n">
-        <v>0.388</v>
+        <v>0.7055</v>
       </c>
       <c r="V17" t="n">
         <v>1.2452</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.541</v>
+        <v>5.9475</v>
       </c>
       <c r="E18" t="n">
-        <v>5.8046</v>
+        <v>5.9995</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2636</v>
+        <v>-0.052</v>
       </c>
       <c r="G18" t="n">
         <v>2.8991</v>
@@ -1858,13 +1858,13 @@
         <v>2.0757</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2833</v>
+        <v>0.6898</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1793</v>
+        <v>0.3741</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1041</v>
+        <v>0.3157</v>
       </c>
       <c r="V18" t="n">
         <v>0.2828</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>5.1398</v>
+        <v>5.1157</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7218</v>
+        <v>2.3321</v>
       </c>
       <c r="F19" t="n">
-        <v>2.418</v>
+        <v>2.7837</v>
       </c>
       <c r="G19" t="n">
         <v>1.9792</v>
@@ -1936,13 +1936,13 @@
         <v>2.0757</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0852</v>
+        <v>1.0611</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0886</v>
+        <v>0.6989</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0035</v>
+        <v>0.3622</v>
       </c>
       <c r="V19" t="n">
         <v>1.8868</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4.3687</v>
+        <v>4.0402</v>
       </c>
       <c r="E20" t="n">
-        <v>4.9975</v>
+        <v>4.5103</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6288</v>
+        <v>-0.4701</v>
       </c>
       <c r="G20" t="n">
         <v>3.3999</v>
@@ -2014,13 +2014,13 @@
         <v>2.0757</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7801</v>
+        <v>0.4516</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.2241</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0688</v>
+        <v>0.2275</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. MARCO CLIMENT</t>
+          <t>V. SANTAMATILDE PERIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>4.2967</v>
+        <v>3.3848</v>
       </c>
       <c r="E21" t="n">
-        <v>3.4002</v>
+        <v>0.2312</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8965</v>
+        <v>3.1536</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8583</v>
+        <v>1.4134</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4236</v>
+        <v>0.1338</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5653</v>
+        <v>1.2796</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7965</v>
+        <v>1.0139</v>
       </c>
       <c r="K21" t="n">
-        <v>1.015</v>
+        <v>0.2324</v>
       </c>
       <c r="L21" t="n">
         <v>0.7815</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6547</v>
+        <v>0.3995</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.4386</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2162</v>
+        <v>0.4981</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4531</v>
+        <v>2.0757</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4002</v>
+        <v>1.4809</v>
       </c>
       <c r="T21" t="n">
-        <v>1.302</v>
+        <v>0.8025</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0982</v>
+        <v>0.6784</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. SANTAMATILDE PERIS</t>
+          <t>F. MARCO CLIMENT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3.9755</v>
+        <v>3.1733</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1081</v>
+        <v>2.6207</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8673</v>
+        <v>0.5526</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4134</v>
+        <v>-0.8583</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1338</v>
+        <v>-1.4236</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2796</v>
+        <v>0.5653</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0139</v>
+        <v>1.7965</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2324</v>
+        <v>1.015</v>
       </c>
       <c r="L22" t="n">
         <v>0.7815</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3995</v>
+        <v>-2.6547</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-2.4386</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4981</v>
+        <v>-0.2162</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1887</v>
+        <v>1.5096</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0757</v>
+        <v>2.4531</v>
       </c>
       <c r="S22" t="n">
-        <v>2.0716</v>
+        <v>1.2768</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6794</v>
+        <v>0.5225</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3921</v>
+        <v>0.7543</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.7275</v>
+        <v>1.9177</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1609</v>
+        <v>-0.966</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8884</v>
+        <v>2.8837</v>
       </c>
       <c r="G23" t="n">
         <v>1.7493</v>
@@ -2248,13 +2248,13 @@
         <v>2.6418</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1293</v>
+        <v>1.3194</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5567</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5726</v>
+        <v>0.5679</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9624</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6401</v>
+        <v>-0.5775</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2166</v>
+        <v>-0.0217</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4236</v>
+        <v>-0.5558</v>
       </c>
       <c r="G25" t="n">
         <v>-0.8923</v>
@@ -2404,13 +2404,13 @@
         <v>0.3774</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1252</v>
+        <v>-0.0626</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2939</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1687</v>
+        <v>0.0365</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>44.26930000000001</v>
+        <v>45.56839999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>30.45489999999999</v>
+        <v>30.455</v>
       </c>
       <c r="F26" t="n">
-        <v>13.8143</v>
+        <v>15.1135</v>
       </c>
       <c r="G26" t="n">
         <v>21.8014</v>
@@ -2482,13 +2482,13 @@
         <v>21.7005</v>
       </c>
       <c r="S26" t="n">
-        <v>8.4299</v>
+        <v>9.7288</v>
       </c>
       <c r="T26" t="n">
-        <v>4.4526</v>
+        <v>4.4524</v>
       </c>
       <c r="U26" t="n">
-        <v>3.9772</v>
+        <v>5.2765</v>
       </c>
       <c r="V26" t="n">
         <v>4.603000000000001</v>
